--- a/assessment_forms/035_ai_reading_comprehension_quiz--assessment_forms.xlsx
+++ b/assessment_forms/035_ai_reading_comprehension_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,12 +917,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'the_biological_functioning_of_the_human_brain.',_'value':_'brain_bio'}</t>
+          <t>the_biological_functioning_of_the_human_brain.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'The biological functioning of the human brain.', 'value': 'brain_bio'}</t>
+          <t>The biological functioning of the human brain.</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'the_historical_development_and_nature_of_artificial_neural_networks.',_'value':_'correct_main'}</t>
+          <t>the_historical_development_and_nature_of_artificial_neural_networks.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'The historical development and nature of artificial neural networks.', 'value': 'correct_main'}</t>
+          <t>The historical development and nature of artificial neural networks.</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'the_risks_of_using_ai_in_the_1950s.',_'value':_'history_risk'}</t>
+          <t>the_risks_of_using_ai_in_the_1950s.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'The risks of using AI in the 1950s.', 'value': 'history_risk'}</t>
+          <t>The risks of using AI in the 1950s.</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'how_to_program_a_transformer_model.',_'value':_'programming'}</t>
+          <t>how_to_program_a_transformer_model.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'How to program a Transformer model.', 'value': 'programming'}</t>
+          <t>How to program a Transformer model.</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'it_allowed_for_the_first_linear_classifications.',_'value':_'linear'}</t>
+          <t>it_allowed_for_the_first_linear_classifications.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'It allowed for the first linear classifications.', 'value': 'linear'}</t>
+          <t>It allowed for the first linear classifications.</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'it_made_multi-layer_networks_computationally_viable.',_'value':_'correct_backprop'}</t>
+          <t>it_made_multi-layer_networks_computationally_viable.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'It made multi-layer networks computationally viable.', 'value': 'correct_backprop'}</t>
+          <t>It made multi-layer networks computationally viable.</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'it_eliminated_all_ai_hallucinations.',_'value':_'no_hallucinate'}</t>
+          <t>it_eliminated_all_ai_hallucinations.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'It eliminated all AI hallucinations.', 'value': 'no_hallucinate'}</t>
+          <t>It eliminated all AI hallucinations.</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'it_was_the_biological_inspiration_for_the_perceptron.',_'value':_'bio_inspire'}</t>
+          <t>it_was_the_biological_inspiration_for_the_perceptron.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'It was the biological inspiration for the Perceptron.', 'value': 'bio_inspire'}</t>
+          <t>It was the biological inspiration for the Perceptron.</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'a_biological_malfunction_in_the_human_brain.',_'value':_'bio_malfunction'}</t>
+          <t>a_biological_malfunction_in_the_human_brain.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'A biological malfunction in the human brain.', 'value': 'bio_malfunction'}</t>
+          <t>A biological malfunction in the human brain.</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'an_ai_generating_plausible-sounding_but_incorrect_information.',_'value':_'correct_hallucinate'}</t>
+          <t>an_ai_generating_plausible-sounding_but_incorrect_information.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'An AI generating plausible-sounding but incorrect information.', 'value': 'correct_hallucinate'}</t>
+          <t>An AI generating plausible-sounding but incorrect information.</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'the_speed_at_which_a_transformer_predicts_tokens.',_'value':_'speed'}</t>
+          <t>the_speed_at_which_a_transformer_predicts_tokens.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'The speed at which a Transformer predicts tokens.', 'value': 'speed'}</t>
+          <t>The speed at which a Transformer predicts tokens.</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'a_limitation_of_the_1950s_perceptron_model.',_'value':_'perceptron_limit'}</t>
+          <t>a_limitation_of_the_1950s_perceptron_model.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'A limitation of the 1950s Perceptron model.', 'value': 'perceptron_limit'}</t>
+          <t>A limitation of the 1950s Perceptron model.</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'they_possess_a_human-like_understanding_of_language.',_'value':_'human_understand'}</t>
+          <t>they_possess_a_human-like_understanding_of_language.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'They possess a human-like understanding of language.', 'value': 'human_understand'}</t>
+          <t>They possess a human-like understanding of language.</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'they_rely_on_statistical_probability_rather_than_true_comprehension.',_'value':_'correct_inference'}</t>
+          <t>they_rely_on_statistical_probability_rather_than_true_comprehension.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'They rely on statistical probability rather than true comprehension.', 'value': 'correct_inference'}</t>
+          <t>They rely on statistical probability rather than true comprehension.</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'they_are_simpler_than_the_models_of_the_1980s.',_'value':_'simple'}</t>
+          <t>they_are_simpler_than_the_models_of_the_1980s.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'They are simpler than the models of the 1980s.', 'value': 'simple'}</t>
+          <t>They are simpler than the models of the 1980s.</t>
         </is>
       </c>
     </row>
